--- a/artfynd/A 20381-2024 artfynd.xlsx
+++ b/artfynd/A 20381-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -783,6 +783,394 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>126170274</v>
+      </c>
+      <c r="B3" t="n">
+        <v>98256</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Hillskaso, Hillskaso, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>483658</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6840267</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>126170189</v>
+      </c>
+      <c r="B4" t="n">
+        <v>78972</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hillskaso, Hillskaso, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>483624</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6840296</v>
+      </c>
+      <c r="S4" t="n">
+        <v>15</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>126170152</v>
+      </c>
+      <c r="B5" t="n">
+        <v>78972</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hillskaso, Hillskaso, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>483613</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6840293</v>
+      </c>
+      <c r="S5" t="n">
+        <v>15</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>126170391</v>
+      </c>
+      <c r="B6" t="n">
+        <v>78972</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hillskaso, Hillskaso, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>483815</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6840217</v>
+      </c>
+      <c r="S6" t="n">
+        <v>15</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 20381-2024 artfynd.xlsx
+++ b/artfynd/A 20381-2024 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>126170274</v>
       </c>
       <c r="B3" t="n">
-        <v>98256</v>
+        <v>98258</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>126170189</v>
       </c>
       <c r="B4" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         <v>126170152</v>
       </c>
       <c r="B5" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>126170391</v>
       </c>
       <c r="B6" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 20381-2024 artfynd.xlsx
+++ b/artfynd/A 20381-2024 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>126170274</v>
       </c>
       <c r="B3" t="n">
-        <v>98258</v>
+        <v>98260</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 20381-2024 artfynd.xlsx
+++ b/artfynd/A 20381-2024 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>126170274</v>
       </c>
       <c r="B3" t="n">
-        <v>98260</v>
+        <v>98262</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 20381-2024 artfynd.xlsx
+++ b/artfynd/A 20381-2024 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>126170274</v>
       </c>
       <c r="B3" t="n">
-        <v>98262</v>
+        <v>98266</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>126170189</v>
       </c>
       <c r="B4" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         <v>126170152</v>
       </c>
       <c r="B5" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>126170391</v>
       </c>
       <c r="B6" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 20381-2024 artfynd.xlsx
+++ b/artfynd/A 20381-2024 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>126170274</v>
       </c>
       <c r="B3" t="n">
-        <v>98266</v>
+        <v>98269</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 20381-2024 artfynd.xlsx
+++ b/artfynd/A 20381-2024 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>126170274</v>
       </c>
       <c r="B3" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>126170189</v>
       </c>
       <c r="B4" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         <v>126170152</v>
       </c>
       <c r="B5" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>126170391</v>
       </c>
       <c r="B6" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
